--- a/artfynd/A 15638-2024 artfynd.xlsx
+++ b/artfynd/A 15638-2024 artfynd.xlsx
@@ -4812,11 +4812,11 @@
         <v>117306237</v>
       </c>
       <c r="B39" t="n">
-        <v>90941</v>
+        <v>91168</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">

--- a/artfynd/A 15638-2024 artfynd.xlsx
+++ b/artfynd/A 15638-2024 artfynd.xlsx
@@ -4908,7 +4908,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 15638-2024 artfynd.xlsx
+++ b/artfynd/A 15638-2024 artfynd.xlsx
@@ -4908,7 +4908,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 15638-2024 artfynd.xlsx
+++ b/artfynd/A 15638-2024 artfynd.xlsx
@@ -4812,7 +4812,7 @@
         <v>117306237</v>
       </c>
       <c r="B39" t="n">
-        <v>91168</v>
+        <v>91182</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 15638-2024 artfynd.xlsx
+++ b/artfynd/A 15638-2024 artfynd.xlsx
@@ -4812,7 +4812,7 @@
         <v>117306237</v>
       </c>
       <c r="B39" t="n">
-        <v>91182</v>
+        <v>91184</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 15638-2024 artfynd.xlsx
+++ b/artfynd/A 15638-2024 artfynd.xlsx
@@ -4812,7 +4812,7 @@
         <v>117306237</v>
       </c>
       <c r="B39" t="n">
-        <v>91184</v>
+        <v>91185</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 15638-2024 artfynd.xlsx
+++ b/artfynd/A 15638-2024 artfynd.xlsx
@@ -4812,7 +4812,7 @@
         <v>117306237</v>
       </c>
       <c r="B39" t="n">
-        <v>91185</v>
+        <v>91194</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 15638-2024 artfynd.xlsx
+++ b/artfynd/A 15638-2024 artfynd.xlsx
@@ -5034,11 +5034,11 @@
         <v>117306656</v>
       </c>
       <c r="B41" t="n">
-        <v>56499</v>
+        <v>56593</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">

--- a/artfynd/A 15638-2024 artfynd.xlsx
+++ b/artfynd/A 15638-2024 artfynd.xlsx
@@ -5034,7 +5034,7 @@
         <v>117306656</v>
       </c>
       <c r="B41" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 15638-2024 artfynd.xlsx
+++ b/artfynd/A 15638-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117161369</v>
+        <v>117306695</v>
       </c>
       <c r="B2" t="n">
-        <v>78444</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>877843</v>
+        <v>877526</v>
       </c>
       <c r="R2" t="n">
-        <v>7383786</v>
+        <v>7383537</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -748,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117161668</v>
+        <v>117305811</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,27 +787,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>877731</v>
+        <v>877404</v>
       </c>
       <c r="R3" t="n">
-        <v>7383544</v>
+        <v>7383434</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -855,17 +844,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Väldigt mycket lunglav</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,6 +873,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -892,15 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117161684</v>
+        <v>117161728</v>
       </c>
       <c r="B4" t="n">
-        <v>79554</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -935,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>877870</v>
+        <v>877628</v>
       </c>
       <c r="R4" t="n">
-        <v>7383622</v>
+        <v>7383457</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -998,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117161272</v>
+        <v>117306546</v>
       </c>
       <c r="B5" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,28 +1004,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1043,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>877762</v>
+        <v>877455</v>
       </c>
       <c r="R5" t="n">
-        <v>7383527</v>
+        <v>7383401</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1073,22 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,43 +1094,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117161612</v>
+        <v>117306578</v>
       </c>
       <c r="B6" t="n">
-        <v>57297</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1160,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>877790</v>
+        <v>877424</v>
       </c>
       <c r="R6" t="n">
-        <v>7383657</v>
+        <v>7383404</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1190,22 +1162,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,6 +1176,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1232,51 +1195,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117161463</v>
+        <v>117305673</v>
       </c>
       <c r="B7" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>877804</v>
+        <v>877438</v>
       </c>
       <c r="R7" t="n">
-        <v>7383663</v>
+        <v>7383402</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1314,12 +1263,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,51 +1296,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117161093</v>
+        <v>117306413</v>
       </c>
       <c r="B8" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1399,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>877679</v>
+        <v>877393</v>
       </c>
       <c r="R8" t="n">
-        <v>7383507</v>
+        <v>7383447</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1429,12 +1365,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,7 +1379,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1462,51 +1397,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117160893</v>
+        <v>117306430</v>
       </c>
       <c r="B9" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1514,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>877851</v>
+        <v>877425</v>
       </c>
       <c r="R9" t="n">
-        <v>7383659</v>
+        <v>7383408</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1544,12 +1466,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,7 +1480,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1577,51 +1498,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117161437</v>
+        <v>117306656</v>
       </c>
       <c r="B10" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1629,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>877847</v>
+        <v>877527</v>
       </c>
       <c r="R10" t="n">
-        <v>7383637</v>
+        <v>7383519</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1659,12 +1571,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,7 +1585,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1692,15 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117161782</v>
+        <v>117161180</v>
       </c>
       <c r="B11" t="n">
-        <v>96755</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,27 +1614,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1736,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>877780</v>
+        <v>877669</v>
       </c>
       <c r="R11" t="n">
-        <v>7383531</v>
+        <v>7383518</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1780,7 +1690,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1799,32 +1708,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117161508</v>
+        <v>117305495</v>
       </c>
       <c r="B12" t="n">
-        <v>57297</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1835,7 +1739,11 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1843,10 +1751,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>877900</v>
+        <v>877560</v>
       </c>
       <c r="R12" t="n">
-        <v>7383541</v>
+        <v>7383447</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1873,22 +1781,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,43 +1813,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117161529</v>
+        <v>117161093</v>
       </c>
       <c r="B13" t="n">
-        <v>57297</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1959,10 +1860,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>877824</v>
+        <v>877679</v>
       </c>
       <c r="R13" t="n">
-        <v>7383669</v>
+        <v>7383507</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1992,27 +1893,18 @@
           <t>2024-05-20</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-05-20</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2031,42 +1923,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117161742</v>
+        <v>117305561</v>
       </c>
       <c r="B14" t="n">
-        <v>79429</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2074,10 +1970,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>877756</v>
+        <v>877389</v>
       </c>
       <c r="R14" t="n">
-        <v>7383535</v>
+        <v>7383441</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2104,12 +2000,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2137,49 +2033,36 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117161394</v>
+        <v>117306729</v>
       </c>
       <c r="B15" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2189,10 +2072,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>877849</v>
+        <v>877375</v>
       </c>
       <c r="R15" t="n">
-        <v>7383643</v>
+        <v>7383448</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2219,12 +2102,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,15 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117161248</v>
+        <v>117306709</v>
       </c>
       <c r="B16" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2268,28 +2146,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>1205</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2297,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>877778</v>
+        <v>878038</v>
       </c>
       <c r="R16" t="n">
-        <v>7383737</v>
+        <v>7383695</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2327,22 +2203,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,37 +2236,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117161728</v>
+        <v>117306237</v>
       </c>
       <c r="B17" t="n">
-        <v>79553</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2413,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>877628</v>
+        <v>877976</v>
       </c>
       <c r="R17" t="n">
-        <v>7383457</v>
+        <v>7383680</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2443,12 +2304,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,37 +2337,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117161710</v>
+        <v>117305247</v>
       </c>
       <c r="B18" t="n">
-        <v>79553</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2519,10 +2375,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>877843</v>
+        <v>878044</v>
       </c>
       <c r="R18" t="n">
-        <v>7383668</v>
+        <v>7383658</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2549,12 +2405,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2582,15 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117161129</v>
+        <v>117305266</v>
       </c>
       <c r="B19" t="n">
-        <v>90481</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2598,21 +2449,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2625,10 +2476,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>877825</v>
+        <v>878031</v>
       </c>
       <c r="R19" t="n">
-        <v>7383668</v>
+        <v>7383720</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2655,12 +2506,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2681,58 +2532,44 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117160941</v>
+        <v>117305202</v>
       </c>
       <c r="B20" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2740,10 +2577,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>877826</v>
+        <v>877726</v>
       </c>
       <c r="R20" t="n">
-        <v>7383674</v>
+        <v>7383459</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2770,12 +2607,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,43 +2640,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117161496</v>
+        <v>117161369</v>
       </c>
       <c r="B21" t="n">
-        <v>57297</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2847,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>877829</v>
+        <v>877843</v>
       </c>
       <c r="R21" t="n">
-        <v>7383533</v>
+        <v>7383786</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2880,27 +2711,18 @@
           <t>2024-05-20</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-05-20</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2919,51 +2741,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117161054</v>
+        <v>117161742</v>
       </c>
       <c r="B22" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2971,10 +2779,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>877843</v>
+        <v>877756</v>
       </c>
       <c r="R22" t="n">
-        <v>7383659</v>
+        <v>7383535</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3034,51 +2842,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117161426</v>
+        <v>117169496</v>
       </c>
       <c r="B23" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3086,10 +2880,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>877824</v>
+        <v>877808</v>
       </c>
       <c r="R23" t="n">
-        <v>7383743</v>
+        <v>7383728</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3137,59 +2931,49 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117161165</v>
+        <v>117161710</v>
       </c>
       <c r="B24" t="n">
-        <v>56486</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3197,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>877739</v>
+        <v>877843</v>
       </c>
       <c r="R24" t="n">
-        <v>7383471</v>
+        <v>7383668</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3241,6 +3025,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3252,54 +3037,44 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117161180</v>
+        <v>117161684</v>
       </c>
       <c r="B25" t="n">
-        <v>56486</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3307,10 +3082,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>877669</v>
+        <v>877870</v>
       </c>
       <c r="R25" t="n">
-        <v>7383518</v>
+        <v>7383622</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3351,6 +3126,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3362,58 +3138,44 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117160981</v>
+        <v>117306509</v>
       </c>
       <c r="B26" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3421,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>877804</v>
+        <v>877960</v>
       </c>
       <c r="R26" t="n">
-        <v>7383623</v>
+        <v>7383727</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3451,12 +3213,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3484,51 +3246,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117161405</v>
+        <v>117161496</v>
       </c>
       <c r="B27" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3536,10 +3285,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>877810</v>
+        <v>877829</v>
       </c>
       <c r="R27" t="n">
-        <v>7383677</v>
+        <v>7383533</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3569,18 +3318,27 @@
           <t>2024-05-20</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-05-20</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3599,51 +3357,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117169467</v>
+        <v>117161508</v>
       </c>
       <c r="B28" t="n">
-        <v>97802</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3651,10 +3396,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>877813</v>
+        <v>877900</v>
       </c>
       <c r="R28" t="n">
-        <v>7383674</v>
+        <v>7383541</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3684,45 +3429,49 @@
           <t>2024-05-20</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-05-20</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117169496</v>
+        <v>117161529</v>
       </c>
       <c r="B29" t="n">
-        <v>79431</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3730,26 +3479,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3757,10 +3507,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>877808</v>
+        <v>877824</v>
       </c>
       <c r="R29" t="n">
-        <v>7383728</v>
+        <v>7383669</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3790,45 +3540,49 @@
           <t>2024-05-20</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-05-20</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117306472</v>
+        <v>117161612</v>
       </c>
       <c r="B30" t="n">
-        <v>97857</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3836,27 +3590,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3864,10 +3618,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>877876</v>
+        <v>877790</v>
       </c>
       <c r="R30" t="n">
-        <v>7383580</v>
+        <v>7383657</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3894,12 +3648,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3908,7 +3672,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3927,15 +3690,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117306709</v>
+        <v>117306303</v>
       </c>
       <c r="B31" t="n">
-        <v>90510</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3943,26 +3701,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3970,10 +3729,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>878038</v>
+        <v>877970</v>
       </c>
       <c r="R31" t="n">
-        <v>7383695</v>
+        <v>7383571</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4003,18 +3762,27 @@
           <t>2024-05-25</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-05-25</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4033,51 +3801,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117305561</v>
+        <v>117306326</v>
       </c>
       <c r="B32" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4085,10 +3840,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>877389</v>
+        <v>877922</v>
       </c>
       <c r="R32" t="n">
-        <v>7383441</v>
+        <v>7383640</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4118,18 +3873,27 @@
           <t>2024-05-25</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-05-25</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4148,15 +3912,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117306724</v>
+        <v>117306351</v>
       </c>
       <c r="B33" t="n">
-        <v>96791</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4164,27 +3923,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4192,10 +3951,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>877959</v>
+        <v>877806</v>
       </c>
       <c r="R33" t="n">
-        <v>7383726</v>
+        <v>7383506</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4225,18 +3984,27 @@
           <t>2024-05-25</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-05-25</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4255,15 +4023,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117305247</v>
+        <v>117161668</v>
       </c>
       <c r="B34" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4271,26 +4034,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4298,10 +4062,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>878044</v>
+        <v>877731</v>
       </c>
       <c r="R34" t="n">
-        <v>7383658</v>
+        <v>7383544</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4328,12 +4092,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4342,7 +4111,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4361,15 +4129,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117306546</v>
+        <v>117161248</v>
       </c>
       <c r="B35" t="n">
-        <v>79590</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4377,26 +4140,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4404,10 +4169,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>877455</v>
+        <v>877778</v>
       </c>
       <c r="R35" t="n">
-        <v>7383401</v>
+        <v>7383737</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4434,12 +4199,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4467,40 +4242,36 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117306303</v>
+        <v>117161272</v>
       </c>
       <c r="B36" t="n">
-        <v>57303</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -4511,10 +4282,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>877970</v>
+        <v>877762</v>
       </c>
       <c r="R36" t="n">
-        <v>7383571</v>
+        <v>7383527</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4541,22 +4312,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4565,6 +4336,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4583,42 +4355,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117305405</v>
+        <v>117161165</v>
       </c>
       <c r="B37" t="n">
-        <v>90517</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4626,10 +4398,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>877930</v>
+        <v>877739</v>
       </c>
       <c r="R37" t="n">
-        <v>7383773</v>
+        <v>7383471</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4656,17 +4428,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Flera Grantickor i samma träd.</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4675,7 +4442,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4694,15 +4460,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117305643</v>
+        <v>117160893</v>
       </c>
       <c r="B38" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4729,12 +4490,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -4746,10 +4507,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>877947</v>
+        <v>877851</v>
       </c>
       <c r="R38" t="n">
-        <v>7383585</v>
+        <v>7383659</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4776,12 +4537,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4809,15 +4570,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117306237</v>
+        <v>117160941</v>
       </c>
       <c r="B39" t="n">
-        <v>91194</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4825,26 +4581,35 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4852,10 +4617,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>877976</v>
+        <v>877826</v>
       </c>
       <c r="R39" t="n">
-        <v>7383680</v>
+        <v>7383674</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4882,12 +4647,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4915,43 +4680,46 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117306351</v>
+        <v>117160981</v>
       </c>
       <c r="B40" t="n">
-        <v>57303</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4959,10 +4727,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>877806</v>
+        <v>877804</v>
       </c>
       <c r="R40" t="n">
-        <v>7383506</v>
+        <v>7383623</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4989,22 +4757,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>16:20</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>16:20</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5013,6 +4771,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5031,47 +4790,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117306656</v>
+        <v>117161054</v>
       </c>
       <c r="B41" t="n">
-        <v>56688</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5079,10 +4837,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>877527</v>
+        <v>877843</v>
       </c>
       <c r="R41" t="n">
-        <v>7383519</v>
+        <v>7383659</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5109,12 +4867,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5123,6 +4881,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5141,43 +4900,46 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117306430</v>
+        <v>117161394</v>
       </c>
       <c r="B42" t="n">
-        <v>57303</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5185,10 +4947,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>877425</v>
+        <v>877849</v>
       </c>
       <c r="R42" t="n">
-        <v>7383408</v>
+        <v>7383643</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5215,12 +4977,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5229,6 +4991,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5247,41 +5010,44 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117306729</v>
+        <v>117161405</v>
       </c>
       <c r="B43" t="n">
-        <v>96791</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5291,10 +5057,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>877375</v>
+        <v>877810</v>
       </c>
       <c r="R43" t="n">
-        <v>7383448</v>
+        <v>7383677</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5321,12 +5087,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5354,41 +5120,44 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117306129</v>
+        <v>117161426</v>
       </c>
       <c r="B44" t="n">
-        <v>96791</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5398,10 +5167,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>878004</v>
+        <v>877824</v>
       </c>
       <c r="R44" t="n">
-        <v>7383772</v>
+        <v>7383743</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5428,12 +5197,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5461,43 +5230,46 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117306326</v>
+        <v>117161437</v>
       </c>
       <c r="B45" t="n">
-        <v>57303</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5505,10 +5277,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>877922</v>
+        <v>877847</v>
       </c>
       <c r="R45" t="n">
-        <v>7383640</v>
+        <v>7383637</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5535,22 +5307,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:06</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:06</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5559,6 +5321,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5577,42 +5340,46 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117305811</v>
+        <v>117161463</v>
       </c>
       <c r="B46" t="n">
-        <v>79561</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5620,10 +5387,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>877404</v>
+        <v>877804</v>
       </c>
       <c r="R46" t="n">
-        <v>7383434</v>
+        <v>7383663</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5650,27 +5417,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Väldigt mycket lunglav</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5698,42 +5450,46 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117306695</v>
+        <v>117169467</v>
       </c>
       <c r="B47" t="n">
-        <v>90660</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5741,10 +5497,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>877526</v>
+        <v>877813</v>
       </c>
       <c r="R47" t="n">
-        <v>7383537</v>
+        <v>7383674</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5771,12 +5527,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5792,55 +5548,58 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117306413</v>
+        <v>117305643</v>
       </c>
       <c r="B48" t="n">
-        <v>57303</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5848,10 +5607,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>877393</v>
+        <v>877947</v>
       </c>
       <c r="R48" t="n">
-        <v>7383447</v>
+        <v>7383585</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -5892,6 +5651,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5910,42 +5670,38 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117305266</v>
+        <v>117161782</v>
       </c>
       <c r="B49" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5953,10 +5709,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>878031</v>
+        <v>877780</v>
       </c>
       <c r="R49" t="n">
-        <v>7383720</v>
+        <v>7383531</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -5983,12 +5739,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6016,47 +5772,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117305495</v>
+        <v>117306129</v>
       </c>
       <c r="B50" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6064,10 +5811,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>877560</v>
+        <v>878004</v>
       </c>
       <c r="R50" t="n">
-        <v>7383447</v>
+        <v>7383772</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6108,6 +5855,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6126,15 +5874,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117305202</v>
+        <v>117306724</v>
       </c>
       <c r="B51" t="n">
-        <v>90907</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6142,26 +5885,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5321</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6169,10 +5913,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>877726</v>
+        <v>877959</v>
       </c>
       <c r="R51" t="n">
-        <v>7383459</v>
+        <v>7383726</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6232,15 +5976,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117305673</v>
+        <v>117306472</v>
       </c>
       <c r="B52" t="n">
-        <v>79597</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6248,26 +5987,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6275,10 +6015,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>877438</v>
+        <v>877876</v>
       </c>
       <c r="R52" t="n">
-        <v>7383402</v>
+        <v>7383580</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -6335,218 +6075,6 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>117306578</v>
-      </c>
-      <c r="B53" t="n">
-        <v>79590</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Puostivaara, Nb</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>877424</v>
-      </c>
-      <c r="R53" t="n">
-        <v>7383404</v>
-      </c>
-      <c r="S53" t="n">
-        <v>1</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Övertorneå</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Hietaniemi</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Viktoria Sturk</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Viktoria Sturk, Marie Persson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>117306509</v>
-      </c>
-      <c r="B54" t="n">
-        <v>79590</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Puostivaara, Nb</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>877960</v>
-      </c>
-      <c r="R54" t="n">
-        <v>7383727</v>
-      </c>
-      <c r="S54" t="n">
-        <v>1</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Övertorneå</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Hietaniemi</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Viktoria Sturk</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Viktoria Sturk, Marie Persson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15638-2024 artfynd.xlsx
+++ b/artfynd/A 15638-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306709</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306237</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117305247</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117305266</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306695</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117305202</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161369</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161742</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117169496</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1697,6 +1747,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117305811</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1798,6 +1853,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161710</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1899,6 +1959,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161728</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2000,6 +2065,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161684</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2101,6 +2171,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306509</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306546</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2303,6 +2383,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306578</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2404,6 +2489,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117305673</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2515,6 +2605,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161496</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2626,6 +2721,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161508</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2737,6 +2837,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161529</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2848,6 +2953,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161612</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2959,6 +3069,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306303</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3070,6 +3185,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306326</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3181,6 +3301,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306351</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3282,6 +3407,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306413</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3383,6 +3513,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306430</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3489,6 +3624,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161668</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3594,6 +3734,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306656</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3707,6 +3852,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161248</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3820,6 +3970,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161272</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3925,6 +4080,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161165</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4030,6 +4190,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161180</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4135,6 +4300,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117305495</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4245,6 +4415,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117160893</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4355,6 +4530,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117160941</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4465,6 +4645,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117160981</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4575,6 +4760,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161054</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4685,6 +4875,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161093</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4795,6 +4990,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161394</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4905,6 +5105,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161405</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5015,6 +5220,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161426</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5125,6 +5335,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161437</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5235,6 +5450,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161463</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5345,6 +5565,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117169467</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5455,6 +5680,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117305561</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5565,6 +5795,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117305643</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5667,6 +5902,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117161782</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5769,6 +6009,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306129</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5871,6 +6116,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306724</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5973,6 +6223,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306729</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6075,8 +6330,66 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306472</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>